--- a/worklist-name-icons.xlsx
+++ b/worklist-name-icons.xlsx
@@ -11,14 +11,16 @@
     <sheet name="ภาพตัวอย่าง" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ไอคอนเฉพาะหน้า" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="เหตุผลส่งต่อ สังคมฯ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="กติกา Dev" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ที่มาของข้อมูล" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="กติกา Dev" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ภาพรวม'!$A$4:$O$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ภาพตัวอย่าง'!$A$4:$D$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ไอคอนเฉพาะหน้า'!$A$4:$G$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'เหตุผลส่งต่อ สังคมฯ'!$A$4:$E$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'กติกา Dev'!$A$4:$B$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ที่มาของข้อมูล'!$A$4:$D$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'กติกา Dev'!$A$4:$B$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1100,7 +1102,7 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>--text-colorfulbadge-purple</t>
+          <t>--text-colorfulbadge-purple · บนการ์ดเขียว (onCard) สีขาว --icon-brandPrimaryButton-on-brand</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -1142,7 +1144,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>ไอคอนไซเรน e911_emergency (filled) · แดง = ฉุกเฉิน · ส้ม = เร่งด่วน</t>
+          <t>ไอคอนไซเรน e911_emergency (filled) · ฉุกเฉิน = แดง · เร่งด่วน = ส้มสด</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1177,7 +1179,7 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>ฉุกเฉิน --text-triage-level1 · เร่งด่วน --text-triage-level2</t>
+          <t>ฉุกเฉิน --text-triage-level1 (แดง) · เร่งด่วน --surface-colorfulbadge-orange-bold (ส้ม)</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -1854,7 +1856,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>หลังชื่อ: (ชื่อเรียก) · privacy_tip ม่วง · psychology_alt — ไอคอนอย่างเดียว ไม่มีวงกลม</t>
+          <t>หลังชื่อ: (ชื่อเรียก) · privacy_tip สีขาว · psychology_alt สีตามระดับ — ไอคอนอย่างเดียว ไม่มีวงกลม</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -3118,6 +3120,547 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ข้อมูลมาจากไหน · ค่าเป็นอะไรถึงแสดง</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>บันทึกที่หน้า/ขั้นไหน · ฟิลด์ในระบบ · ค่าที่ทำให้ไอคอนขึ้น</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>กลุ่ม</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>ไอคอน</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>ข้อมูลมาจาก (บันทึกที่ไหน · ฟิลด์)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>ค่าที่ทำให้แสดง</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ไอคอนกลาง (ทุกหน้ารายชื่อ)</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>ชื่อที่ต้องการให้เรียก</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>เวชระเบียน › ข้อมูลส่วนตัว ช่อง "ชื่อที่ต้องการให้เรียก" → patientProfiles.preferredName</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>ไม่ใช่ค่าว่าง (เช่น "ลี") · ติ๊ก "ต้องการให้เรียกนามแฝง" (callByAlias) มีผลแค่ตอนเรียกคิว ไม่เปลี่ยนหน้าตา</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ไอคอนกลาง (ทุกหน้ารายชื่อ)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>คัดลอกชื่อ</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>ชื่อ-นามสกุลของแถวนั้น (prop name)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>แสดงเสมอ เว้นหน้าที่ส่ง copyable = false</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>ไอคอนกลาง (ทุกหน้ารายชื่อ)</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>ผู้รับบริการรายใหม่</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>เวชระเบียน › ประเภทผู้ป่วย → patientProfiles.patientType · รายชื่อสมัครผ่าน Mobile App (mobileAppSignups.js)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>patientType = "ผู้ป่วยใหม่" หรือ HN อยู่ในรายชื่อมาครั้งแรกจาก Mobile App · หน้าที่มีเกณฑ์เองส่ง isNew = true</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>ไอคอนกลาง (ทุกหน้ารายชื่อ)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>ค้างชำระ</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>คิวการเงิน /finance (financeLiveQueue) + คำขอลดหย่อน (financeApprovals)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>ยอดรวมค้าง &gt; 0 จาก: ① Visit ก่อนวันนี้ที่ยอดค้าง (outstandingOf) &gt; 0 ② priorDebts[].amount &gt; 0 ③ Visit วันนี้ที่ส่งเคสลดหย่อนแล้ว สถานะรอนักสังคม / รอ ผอ.ศูนย์ / ไม่อนุมัติ (อนุมัติแล้ว = ยอดหลังหัก &gt; 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>ไอคอนกลาง (ทุกหน้ารายชื่อ)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>นัดปรึกษาวันนี้</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>นัดปรึกษา Telemedicine (telemedConsults.js) ที่สร้างจากแท็บ/ปุ่ม "ส่งปรึกษา"</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>consult.hn = HN นี้ · consult.dateKey = วันนี้ · ผู้ใช้ปัจจุบันเป็นผู้ขอ (sent) หรือผู้ให้คำปรึกษา (received) · หน้านั้นเปิด showConsult</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>ไอคอนกลาง (ทุกหน้ารายชื่อ)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>โรคที่อ่อนไหว</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>เวชระเบียน › โรคประจำตัว (mrPatients.chronicDiseases) · Problem list ของแพทย์ (treatmentProblemList) · ทะเบียนยา ARV (hivStiVisits)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>รหัส B20–B24 หรือชื่อมีคำ HIV/เอชไอวี · รหัส C50 หรือชื่อมีคำ มะเร็งเต้านม · Problem list สถานะ active/watch · ARV สถานะ here/ltfu · และ role มีสิทธิ์ข้อมูลลับ (canSeeConfidential = true)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>ไอคอนกลาง (ทุกหน้ารายชื่อ)</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>ฉุกเฉิน (แดง)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>จุดคัดกรอง OPD › ขั้น "ซักประวัติ" ช่อง ระดับการคัดแยก (Triage ESI) → screening.symptom.triage</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>triage.level = 1 หรือ 2 → ฉุกเฉิน (แดง)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>ไอคอนกลาง (ทุกหน้ารายชื่อ)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>เร่งด่วน (ส้ม)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>จุดคัดกรอง OPD › ขั้น "ซักประวัติ" ช่อง ระดับการคัดแยก (Triage ESI) → screening.symptom.triage</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>triage.level = 3 → เร่งด่วน (ส้ม)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>ไอคอนกลาง (ทุกหน้ารายชื่อ)</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>มีอาการทางจิต (OAS)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>จุดคัดกรอง OPD › ขั้น "แบบประเมิน" แถว แบบประเมินพฤติกรรมก้าวร้าว (OAS) → screening.behaviour.oasDetail</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>oasDetail.status = "has" (มีอาการทางจิต) และระดับ = เหลือง / ส้ม / แดง (ไม่ระบุระดับ → คิดจากอาการที่ติ๊กสูงสุด) · เขียว/ไม่มีอาการ = ไม่แสดง</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>ไอคอนเฉพาะหน้า</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>ก้าวร้าวพิเศษ</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>จุดคัดกรอง OPD › ขั้น "แบบประเมิน" → screening.behaviour.specialAggression</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>specialAggression = true และหมวดไม่ถูกข้าม · ⚠ ช่องติ๊กถูกถอดจากหน้าคัดกรองแล้ว (16 ต.ค. 69) — ขึ้นเฉพาะข้อมูลเก่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>ไอคอนเฉพาะหน้า</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>ตั้งครรภ์</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>จุดคัดกรอง OPD › ขั้น "ซักประวัติ" ช่อง สถานะการตั้งครรภ์ + LMP → screening.pregnancyStatus · lmp</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>pregnancyStatus = "กำลังตั้งครรภ์" (อายุครรภ์คิดจาก LMP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>ไอคอนเฉพาะหน้า</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>ความเสี่ยงสุขภาพจิต</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>เยี่ยมบ้าน › หน้าบันทึกการเยี่ยม แบบประเมิน 2Q plus / 9Q → ประวัติ homevisitMentalRisk (ผลล่าสุด)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>เหลือง = 2Q plus บวก หรือ 9Q 7–12 · ส้ม = 9Q 13–18 · แดง = 2Q plus ข้อ 3 "มี" หรือ 9Q ข้อ 9 หรือ 9Q ≥ 19 · ไม่พบความเสี่ยง = ไม่แสดง</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>ไอคอนเฉพาะหน้า</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>กลุ่มโภชนาการ</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>งานโภชนาการ › เคสที่รับส่งต่อ ช่องกลุ่มเป้าหมาย → row.group</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>child = เด็ก · pregnant = หญิงตั้งครรภ์ · elderly = ผู้สูงอายุ · adult = ไม่มีไอคอน</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>ไอคอนเฉพาะหน้า</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>เหตุผลการส่งต่อ (33 แบบ)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>ป๊อปอัปส่งต่อถึงงานสังคมสงเคราะห์ (ติ๊กเหตุผล) · เวชระเบียน/วัคซีน/คัดกรอง (เด็กเสี่ยง) → row.referralWatchTags · referralOtherReason · childAlerts</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>1 ค่าที่ติ๊ก = 1 ไอคอน · เด็กเสี่ยงเฉพาะอายุ &lt; 18 ปี: ไม่มีสิทธิการรักษา · ไม่ได้วัคซีนตามวัย · สงสัยถูกกระทำรุนแรง</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>ไอคอนเฉพาะหน้า</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>ป้าย "ใหม่"</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>คิวเวชระเบียน › แถว walk-in ที่ยังไม่มี HN</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>isNewPatientRow(row) = true</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>ไอคอนเฉพาะหน้า</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>อยู่ในการติดตามการดูแล</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>คลินิกโรคเรื้อรัง › ขึ้นทะเบียนผู้ป่วย (chronic registration) + ประวัติการมาคลินิก</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>มีทะเบียนแล้ว หรือจำนวนครั้งที่มาคลินิก &gt; 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>ไอคอนเฉพาะหน้า</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Red Flag พัฒนาการ</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>คลินิกเด็กดี › แบบประเมินพัฒนาการ DSPM / DAIM (developmentClinic.js)</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>พบพัฒนาการล่าช้า และเข้าเกณฑ์ Red Flag (getDevRedFlag → active = true)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>ไอคอนเฉพาะหน้า</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>มาฟังผล</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>ป๊อปอัป "ยืนยันรับผู้ป่วย" ที่จุดคัดกรอง ติ๊ก "มาฟังผล" → resultsVisits.js</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>มีแถว resultsVisit ของ HN วันนี้</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ไอคอนเฉพาะหน้า</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>ข้อมูลลับ (นักเรียน)</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>ทะเบียนนักเรียน › ข้อมูลนักเรียน → student.confidential</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>confidential = true</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>ไอคอนเฉพาะหน้า</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>เสียชีวิต</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>เวชระเบียน › สถานะการมีชีวิต → patient.lifeStatus</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>lifeStatus = "deceased"</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ไอคอนเฉพาะหน้า</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>กำลังดู</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>สถานะหน้าจอ (ไม่ได้มาจากข้อมูลผู้ป่วย)</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>แถวที่เปิดแผงรายละเอียดอยู่</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>ไอคอนเฉพาะหน้า</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>ป้าย HN</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>HN ของแถว</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>แสดงทุกแถว</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:D26"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/worklist-name-icons.xlsx
+++ b/worklist-name-icons.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ภาพรวม'!$A$4:$O$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ภาพตัวอย่าง'!$A$4:$D$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ไอคอนเฉพาะหน้า'!$A$4:$G$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ไอคอนเฉพาะหน้า'!$A$4:$G$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'เหตุผลส่งต่อ สังคมฯ'!$A$4:$E$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ที่มาของข้อมูล'!$A$4:$D$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'กติกา Dev'!$A$4:$B$16</definedName>
@@ -1563,7 +1563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2147,42 +2147,153 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>คิวทันตกรรม /clinic/dental</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>lock filled ม่วง 16px</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>ข้อมูลลับ (§1.4.2)</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>dentalVisits.confidential = true</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>ข้อมูลลับ · Visit นี้ตั้งเป็นข้อมูลลับ</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>--text-colorfulbadge-purple · 16×24</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>NameMark · DentalQueuePage.jsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>คิวห้องปฏิบัติการ /lab/queue</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>lock filled ม่วง 16px</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>ผลตรวจเป็นความลับ (HIV / VCT)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>labCatalog confidential = true · ชื่อแสดง "ปกปิด (VCT)"</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>ผลตรวจเป็นความลับ · ชื่อและ HN ถูกปกปิด</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>--text-colorfulbadge-purple · 16×24</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>NameMark · LabQueuePage.jsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>คิวทันตกรรม /clinic/dental</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>pregnant_woman filled ชมพู 16px</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>หญิงตั้งครรภ์</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>row.patientType = anc</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>หญิงตั้งครรภ์ · ระวังยาและหัตถการ</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>--text-colorfulbadge-pink · 16×24</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>NameMark · DentalQueuePage.jsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
           <t>การจัดการความยินยอม</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>ป้าย "HN …" เทา</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>HN ของผู้รับบริการ</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>ทุกแถว</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>ไม่มี</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>ColorfulBadge grey small</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>ConsentManagementPage.jsx:1024</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G19"/>
+  <autoFilter ref="A4:G22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/worklist-name-icons.xlsx
+++ b/worklist-name-icons.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ภาพรวม'!$A$4:$O$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ภาพตัวอย่าง'!$A$4:$D$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ไอคอนเฉพาะหน้า'!$A$4:$G$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ไอคอนเฉพาะหน้า'!$A$4:$G$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'เหตุผลส่งต่อ สังคมฯ'!$A$4:$E$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ที่มาของข้อมูล'!$A$4:$D$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'กติกา Dev'!$A$4:$B$16</definedName>
@@ -1563,7 +1563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2258,42 +2258,338 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
+          <t>คิวเอกซเรย์ /xray/queue</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>flag filled แดง 14px</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>แพ้สารทึบรังสี</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>xrayOrders contrast = true และ allergy.has = true</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>แพ้&lt;สาร&gt; — &lt;อาการ&gt;</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>--text-statusbadge-error</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>XrayQueuePage.jsx RowWarnGlyphs</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>คิวเอกซเรย์ /xray/queue</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>pregnant_woman ส้ม 14px</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>ตั้งครรภ์ — ระวังการฉายรังสี</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>xrayOrders pregnancy.status = ตั้งครรภ์</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>ตั้งครรภ์ (LMP …) — ระวังการฉายรังสี</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>--text-statusbadge-warning</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>XrayQueuePage.jsx RowWarnGlyphs</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>คิวเอกซเรย์ /xray/queue</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>radiology น้ำเงิน 14px</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>ฟิล์มออกแล้ว รอบันทึกผล</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>xrayOrders filmIssuedAt มีค่า</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>ฟิล์มออกแล้ว &lt;เวลา&gt;</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>--text-statusbadge-info</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>XrayQueuePage.jsx RowWarnGlyphs</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>คิวเอกซเรย์ /xray/queue</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>output ส้ม 14px</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>ส่งตรวจภายนอก (Referral)</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>xrayOrders referralOnly = true</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>ส่งตรวจภายนอก — ไม่ได้ตรวจในศูนย์ฯ</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>--text-statusbadge-warning</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>XrayQueuePage.jsx RowWarnGlyphs</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>คิวเอกซเรย์ /xray/queue</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>content_copy ส้ม 14px</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>เคยถ่ายซ้ำในช่วงเวลาเตือน (§1.12.5.9)</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>duplicateWarning(examId, ประวัติเอกซเรย์ของ HN)</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>ข้อความเตือนถ่ายซ้ำ</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>--text-statusbadge-warning</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>XrayQueuePage.jsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>คิวเอกซเรย์ /xray/queue</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>edit น้ำเงิน 14px</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>รังสีแพทย์แก้ไขรายละเอียดการส่งตรวจ (§1.12.5.6)</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>xrayOrders amendedByRadiology = true</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>เวลา ผู้แก้ — เหตุผล ทุกครั้ง</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>--text-statusbadge-info</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>XrayQueuePage.jsx RowWarnGlyphs</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>คิวคัดกรองงานพัฒนาการ /clinic/mental-health/screening</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>flag filled แดง 16px</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>พัฒนาการล่าช้า (red flag)</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>redFlag = true (ล่าช้า ≥ 2 ด้าน หรือติ๊กอาการเด่นชัด)</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>สิ่งที่พบ · ที่มา</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>--text-danger-default · 16×24</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>DevSpecialMarks.jsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>คิวคัดกรองงานพัฒนาการ /clinic/mental-health/screening</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>monitor_weight filled ส้ม 16px</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>น้ำหนักแรกเกิดน้อย</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>birthWeight &lt; 2.5 กก.</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>น้ำหนักแรกเกิด N กรัม · คู่มือ DAIM</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>--text-colorfulbadge-orange · 16×24</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>DevSpecialMarks.jsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
           <t>การจัดการความยินยอม</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>ป้าย "HN …" เทา</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>HN ของผู้รับบริการ</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>ทุกแถว</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>ไม่มี</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>ColorfulBadge grey small</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>ConsentManagementPage.jsx:1024</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G22"/>
+  <autoFilter ref="A4:G30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/worklist-name-icons.xlsx
+++ b/worklist-name-icons.xlsx
@@ -2263,7 +2263,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>flag filled แดง 14px</t>
+          <t>flag filled แดง 16px</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>XrayQueuePage.jsx RowWarnGlyphs</t>
+          <t>NameMark · XrayQueuePage.jsx RowWarnGlyphs</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>pregnant_woman ส้ม 14px</t>
+          <t>pregnant_woman filled ส้ม 16px</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>XrayQueuePage.jsx RowWarnGlyphs</t>
+          <t>NameMark · XrayQueuePage.jsx RowWarnGlyphs</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>radiology น้ำเงิน 14px</t>
+          <t>radiology filled น้ำเงิน 16px</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>XrayQueuePage.jsx RowWarnGlyphs</t>
+          <t>NameMark · XrayQueuePage.jsx RowWarnGlyphs</t>
         </is>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>output ส้ม 14px</t>
+          <t>output filled ส้ม 16px</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>XrayQueuePage.jsx RowWarnGlyphs</t>
+          <t>NameMark · XrayQueuePage.jsx RowWarnGlyphs</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>content_copy ส้ม 14px</t>
+          <t>content_copy filled ส้ม 16px</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>edit น้ำเงิน 14px</t>
+          <t>edit filled น้ำเงิน 16px</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>XrayQueuePage.jsx RowWarnGlyphs</t>
+          <t>NameMark · XrayQueuePage.jsx RowWarnGlyphs</t>
         </is>
       </c>
     </row>

--- a/worklist-name-icons.xlsx
+++ b/worklist-name-icons.xlsx
@@ -12,7 +12,6 @@
     <sheet name="ไอคอนเฉพาะหน้า" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="เหตุผลส่งต่อ สังคมฯ" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="ที่มาของข้อมูล" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="กติกา Dev" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ภาพรวม'!$A$4:$O$14</definedName>
@@ -20,7 +19,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ไอคอนเฉพาะหน้า'!$A$4:$G$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'เหตุผลส่งต่อ สังคมฯ'!$A$4:$E$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ที่มาของข้อมูล'!$A$4:$D$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'กติกา Dev'!$A$4:$B$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1671,7 +1669,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>pregnant_woman สีชมพู</t>
+          <t>pregnant_woman filled สีชมพู 16px</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -1691,7 +1689,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>--text-colorfulbadge-pink · ไอคอน 18 ไม่มีวงกลม</t>
+          <t>--text-colorfulbadge-pink · ไอคอน 16 filled · กรอบ 16×24</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -1930,7 +1928,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>schedule สีเขียวแบรนด์ 14px</t>
+          <t>schedule filled สีเขียวแบรนด์ 16px</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1967,7 +1965,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>flag filled สีแดง 20px</t>
+          <t>flag filled สีแดง 16px</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -1982,17 +1980,17 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>⚠ ใช้ title ของเบราว์เซอร์ (ผิดกติกา tooltip) — Red Flag · เหตุผล · ส่งต่อ</t>
+          <t>Red Flag · สิ่งที่พบ · ส่งต่อ (Tooltip สีขาว)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>--text-danger-default · 20px (ใหญ่กว่าชุดกลาง)</t>
+          <t>--text-danger-default · 16×24</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>src/pages/clinic/immunization/ImmunizationQueuePage.jsx:170 (RedFlagMark)</t>
+          <t>NameMark · ImmunizationQueuePage.jsx (RedFlagMark)</t>
         </is>
       </c>
     </row>
@@ -4060,193 +4058,4 @@
   <autoFilter ref="A4:D26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>กติกาที่ Dev ต้องทำตาม</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>ใช้ร่วมกับ CLAUDE.md (design token · icon · tooltip)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>หัวข้อ</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>กติกา</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>ที่อยู่โค้ด</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>ทุกสัญลักษณ์รวมใน MaskedWorklistName — ห้ามวาดไอคอนหลังชื่อเองในหน้า · เพิ่มเกณฑ์ใหม่ที่ data function (เช่น SENSITIVE_DIAGNOSES) แล้วทุก worklist ได้พร้อมกัน</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>ลำดับ</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>ชื่อ → (ชื่อเรียก) → คัดลอก → ใหม่ → ค้างชำระ → นัดปรึกษา → โรคอ่อนไหว → ฉุกเฉิน/เร่งด่วน → อาการทางจิต → extraMarks</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>ระยะห่าง</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>gap 4px (--dim-space-100) · ปุ่มคัดลอกดึงชิดชื่อ −2px (--dim-space-050)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>ขนาดไอคอน</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>กรอบกว้าง 16 (--dim-size-300) สูง 24 (--dim-size-500) ทุกตัว · ไอคอน Material Symbols แบบ filled (fill=1, weight 500)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>การตัดคำ</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>สัญลักษณ์ทุกตัว shrink-0 — ชื่อจริงเป็นส่วนเดียวที่ตัด … เมื่อคอลัมน์แคบ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Tooltip</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>variant light (การ์ดขาว) ทุกตัว · ห้ามใช้ title ของเบราว์เซอร์ · เนื้อหาเป็น TooltipGroups (หัวข้อ → บรรทัดรอง → กลุ่ม label/value) · ในเซลล์ Table ต้อง memo content (outstandingDebtTip cache ต่อ HN · ConsultKindTag useMemo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>มือถือ / แท็บเล็ต</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>ไอคอนมี tabIndex 0 + role img + aria-label → แตะ/focus เปิด tooltip ได้ (hover-only ต้องแตะถึง)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>คลิกไม่ทะลุ</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>ปุ่มคัดลอก preventDefault + stopPropagation (ไม่เปิดแถว/ลิงก์) · ชื่อที่เป็นลิงก์ stopPropagation ตาม prop stopPropagation</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>ข้อมูล real-time</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>ค้างชำระคำนวณใหม่เมื่อคิวการเงินเปลี่ยน (financeLiveVersion) หรือคำขออนุมัติเปลี่ยน · ผลคัดกรองที่พยาบาลบันทึกจริงชนะ mock เสมอ</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>สิทธิ์</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>โรคอ่อนไหวซ่อนสำหรับ role ที่ไม่มีสิทธิ์ข้อมูลลับ · สัญลักษณ์อื่นทุก role เห็น</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>ที่อื่นที่ใช้ชุดเดียวกัน</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>PatientCard (การ์ดเขียว) ใช้ SensitiveDiagnosisMark / PsychMark หน้าตาเดียวกับรายชื่อ (ไม่มีวงกลมพื้น) · ค้างชำระเป็นป้าย "ค้างชำระ" (OutstandingDebtBadge) แถว HN·VN · หน้าเปิด Visit เป็น OutstandingDebtAlert</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>props ปิด/เปิด</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>copyable=false ปิดคัดลอก · isNew true/false บังคับป้ายใหม่ · newTip tooltip ป้ายใหม่ · showDebt=false ปิดค้างชำระ · showConsult=true เปิดป้ายปรึกษา · extraMarks ไอคอนเพิ่ม · preferredName ส่งชื่อเรียกเอง</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:B16"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/worklist-name-icons.xlsx
+++ b/worklist-name-icons.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ภาพรวม'!$A$4:$O$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ภาพตัวอย่าง'!$A$4:$D$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ไอคอนเฉพาะหน้า'!$A$4:$G$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ไอคอนเฉพาะหน้า'!$A$4:$G$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'เหตุผลส่งต่อ สังคมฯ'!$A$4:$E$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ที่มาของข้อมูล'!$A$4:$D$26</definedName>
   </definedNames>
@@ -1561,7 +1561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2441,37 +2441,37 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>คิวเอกซเรย์ /xray/queue</t>
+          <t>คิวคัดกรองงานพัฒนาการ /clinic/mental-health/screening</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>edit filled น้ำเงิน 16px</t>
+          <t>flag filled แดง 16px</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>รังสีแพทย์แก้ไขรายละเอียดการส่งตรวจ (§1.12.5.6)</t>
+          <t>พัฒนาการล่าช้า (red flag)</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>xrayOrders amendedByRadiology = true</t>
+          <t>redFlag = true (ล่าช้า ≥ 2 ด้าน หรือติ๊กอาการเด่นชัด)</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>เวลา ผู้แก้ — เหตุผล ทุกครั้ง</t>
+          <t>สิ่งที่พบ · ที่มา</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>--text-statusbadge-info</t>
+          <t>--text-danger-default · 16×24</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>NameMark · XrayQueuePage.jsx RowWarnGlyphs</t>
+          <t>DevSpecialMarks.jsx</t>
         </is>
       </c>
     </row>
@@ -2483,27 +2483,27 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>flag filled แดง 16px</t>
+          <t>monitor_weight filled ส้ม 16px</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>พัฒนาการล่าช้า (red flag)</t>
+          <t>น้ำหนักแรกเกิดน้อย</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>redFlag = true (ล่าช้า ≥ 2 ด้าน หรือติ๊กอาการเด่นชัด)</t>
+          <t>birthWeight &lt; 2.5 กก.</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>สิ่งที่พบ · ที่มา</t>
+          <t>น้ำหนักแรกเกิด N กรัม · คู่มือ DAIM</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>--text-danger-default · 16×24</t>
+          <t>--text-colorfulbadge-orange · 16×24</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -2515,79 +2515,42 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>คิวคัดกรองงานพัฒนาการ /clinic/mental-health/screening</t>
+          <t>การจัดการความยินยอม</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>monitor_weight filled ส้ม 16px</t>
+          <t>ป้าย "HN …" เทา</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>น้ำหนักแรกเกิดน้อย</t>
+          <t>HN ของผู้รับบริการ</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>birthWeight &lt; 2.5 กก.</t>
+          <t>ทุกแถว</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>น้ำหนักแรกเกิด N กรัม · คู่มือ DAIM</t>
+          <t>ไม่มี</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>--text-colorfulbadge-orange · 16×24</t>
+          <t>ColorfulBadge grey small</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>DevSpecialMarks.jsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>การจัดการความยินยอม</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>ป้าย "HN …" เทา</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>HN ของผู้รับบริการ</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>ทุกแถว</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>ไม่มี</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>ColorfulBadge grey small</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
           <t>ConsentManagementPage.jsx:1024</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G30"/>
+  <autoFilter ref="A4:G29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/worklist-name-icons.xlsx
+++ b/worklist-name-icons.xlsx
@@ -12,6 +12,7 @@
     <sheet name="ไอคอนเฉพาะหน้า" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="เหตุผลส่งต่อ สังคมฯ" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="ที่มาของข้อมูล" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ประวัติการแก้ไข" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ภาพรวม'!$A$4:$O$14</definedName>
@@ -479,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -513,6 +514,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -593,7 +595,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -670,7 +672,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -747,7 +749,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -824,7 +826,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -899,240 +901,232 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>สภาพที่มาใช้บริการ</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>เปลนอน airline_seat_flat · นั่งรถเข็น accessible (filled สีน้ำเงิน) · อื่นๆ = คำที่กรอกเป็นตัวแดง</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>ผู้รับบริการมาด้วยเปลนอน / รถเข็น — จัดคิวก่อน</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>เวชระเบียน ขั้น "หมายเหตุและ Flag" เลือก เปลนอน / นั่งรถเข็น / อื่นๆ</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>เลือก "เดิน" · ยังไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>arrivalMobilityOf · src/data/registrationHandoff.js</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>TooltipGroups: "สภาพที่มาใช้บริการ" · สภาพ · ที่มา</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>ไม่มี</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>--text-info-default · อื่นๆ --text-danger-default</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>ไอคอน 14</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>src/components/badge/ArrivalMobilityMark.jsx</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>ผู้ใช้ 23 ต.ค. 69 · ลำดับคิว ฉุกเฉิน → เปลนอน → รถเข็น → เร่งด่วน</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>ค้างชำระ</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>ไอคอน payments (filled) สีส้ม</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>มียอดค้างชำระจากการมารับบริการครั้งก่อน (มติ คทง.8 ข้อ 2.1.5) — เตือนทุกจุดบริการจนกว่าจะชำระ ไม่บล็อกบริการ</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>outstandingDebtOf(hn).total &gt; 0 = (1) ยอดค้างของ Visit ที่ไม่ใช่วันนี้ + (2) priorDebts ที่ติดมากับแถว + (3) เคสลดหย่อนที่ส่งแล้วแต่ยังไม่อนุมัติ/ไม่อนุมัติ (นับเต็มยอดแม้ Visit วันนี้) · อนุมัติแล้ว = เหลือยอดหลังหัก</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>ผู้รับบริการรายใหม่ (ไม่มีครั้งก่อน) · ชำระที่การเงินแล้ว (ป้ายหายเอง) · ยอด Visit วันนี้ที่ยังไม่ถึงจุดชำระ · ลดหย่อนอนุมัติ 100% · หน้าส่ง showDebt={false}</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>outstandingDebtOf · src/data/outstandingDebts.js ← financeLiveRows() (src/data/financeLiveQueue.js = คิว /finance) + listFinanceApprovals()</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>Tooltip light (กว้าง 360): หัวข้อ "ยอดค้างชำระ" · บรรทัดรอง "จากการมารับบริการครั้งก่อน · แจ้งชำระที่การเงิน" · ตาราง วันที่ | Visit (VN) | ยอด (ชิดขวา) · บรรทัดท้าย "รวม N รายการ" + ยอดรวมตัวหนาสีแดง</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>ไม่มี (tabIndex 0 → focus/แตะเปิด tooltip ได้)</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>ไอคอน --surface-colorfulbadge-orange-bold · ยอดรวม --text-danger-default</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>ไอคอน 16px · กรอบ 16×24</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>ไอคอน 14px · กรอบ 16×24</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>src/components/alert/OutstandingDebtAlert.jsx (OutstandingDebtMark · outstandingDebtTip)</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>showDebt (default true)</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>ราว 1 ใน 3 ของคิวการเงิน (buildPriorDebts)</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>17–18 ต.ค. 69</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>นัดปรึกษาวันนี้</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>ป้าย ColorfulBadge "ขอคำปรึกษา" (คราม) หรือ "ให้คำปรึกษา" (ม่วง)</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>มีนัดปรึกษา Telemedicine วันนี้ — ฉันเป็นผู้ขอ / ฉันเป็นผู้ให้คำปรึกษา</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>ปิดเป็นค่าเริ่มต้น (showConsult=false) · แสดงเฉพาะหน้าที่ส่ง showConsult={true} · มีหลายนัด = นัดที่เร็วที่สุด 1 ป้าย</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>หน้าคิวทั่วไป (สับสนกับการรับบริการ — ดูที่แท็บ "ปรึกษา" แทน)</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>myConsultsForHnToday · src/data/telemedConsults.js</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>TooltipGroups: หัวข้อ ชนิดป้าย · บรรทัดรอง วันนี้ · ช่วงเวลา · กลุ่ม "การนัดปรึกษา": ประเภท · ผู้ให้/ผู้ขอคำปรึกษา</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>ไม่มี</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>sent = indigo · received = purple</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>size xsmall · width hug</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>src/components/badge/ConsultKindTag.jsx</t>
         </is>
       </c>
-      <c r="M10" s="5" t="inlineStr">
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>showConsult (default false)</t>
         </is>
       </c>
-      <c r="N10" s="5" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O10" s="5" t="inlineStr">
+      <c r="O11" s="5" t="inlineStr">
         <is>
           <t>14 ต.ค. 69</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>โรคที่อ่อนไหว (ข้อมูลลับ)</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>ไอคอน privacy_tip (filled) สีม่วง</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>ผู้รับบริการมีโรคที่อ่อนไหว เช่น HIV · มะเร็งเต้านม — hover บอกเฉพาะรหัส ICD-10 ไม่บอกชื่อโรค</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>sensitiveDiagnosesFor(hn) มีผล: โรคประจำตัวในเวชระเบียน (chronicDiseases) · Problem list ของแพทย์ที่ active/watch · ผู้อยู่ในระบบยา ARV · seed · AND role มีสิทธิ์ข้อมูลลับ (canSeeConfidential)</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>ไม่มีโรคในรายการ · role ไม่มีสิทธิ์ข้อมูลลับ (ซ่อนไอคอนด้วย เพราะไอคอนเองก็บอกได้ว่ามีโรคลับ)</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>sensitiveDiagnosesFor · src/data/sensitiveDiagnoses.js (SENSITIVE_DIAGNOSES: hiv B24 · breast-cancer C50.9) · getTreatmentAccess()</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Tooltip light ข้อความรหัสอย่างเดียว เช่น "B24" หรือ "B24 · C50.9"</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>ไม่มี</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>--text-colorfulbadge-purple · บนการ์ดเขียว (onCard) สีขาว --icon-brandPrimaryButton-on-brand</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>ไอคอน 16 · กรอบ 16×24 ทุกที่ (ไม่มีวงกลม)</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>src/components/privacy/SensitiveDiagnosisMark.jsx</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>ไม่มี (เปิดเสมอเมื่อเข้าเกณฑ์)</t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>67-00002 (มะเร็งเต้านม)</t>
-        </is>
-      </c>
-      <c r="O11" s="4" t="inlineStr">
-        <is>
-          <t>30 ก.ย. · 7 ต.ค. 69</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -1207,154 +1201,292 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>มีอาการทางจิต (OAS)</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>ไอคอน psychology_alt (filled) สีตามระดับ OAS เหลือง / ส้ม / แดง</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>พยาบาลคัดกรองประเมิน OAS แล้วพบอาการทางจิต — ต้องเฝ้าระวังขณะรอตรวจ</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>psychSymptomsOf(hn): behaviour.oasDetail.status = "has" และระดับ ≠ เขียว (ระดับจาก level หรือคำนวณจากอาการที่ติ๊ก: แดง &gt; ส้ม &gt; เหลือง)</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>ไม่มีอาการ / ยังไม่ประเมิน / ระดับเขียว</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>psychSymptomsOf · src/data/psychScreening.js ← OAS_LEVELS (src/data/addictionScreeningForms.js) · seed PSYCH_OAS_SEED (opdScreeningSeed.js)</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>TooltipGroups: หัวข้อ "มีอาการทางจิต (OAS)" · บรรทัดรอง "ระดับส้ม · N อาการ" · แถว อาการที่พบ · หมายเหตุ · ที่มา · กลุ่ม "การเฝ้าระวัง": ขณะรอตรวจ</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>สัญญาณชีพวิกฤต</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>ไอคอน monitor_heart (filled) แดง = วิกฤต · ส้ม = ผิดปกติหลายค่า (Early Warning)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>สัญญาณชีพจากจุดคัดกรองเกินเกณฑ์ — แจ้งแพทย์ก่อนส่งเข้าห้องตรวจ</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>แดง: ≥ 1 ค่าระดับอันตราย · ส้ม: ≥ 2 ค่าระดับเฝ้าระวัง</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>ค่าปกติ · ยังไม่คัดกรอง · ตอนนี้ขึ้นเฉพาะรายที่มีไอคอนฉุกเฉิน/เร่งด่วนด้วย (รอยืนยัน)</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>สัญญาณชีพจุดคัดกรองรอบล่าสุด</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>TooltipGroups: ค่าที่เกินเกณฑ์ · ที่มา</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>ไม่มี</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>--text-colorfulbadge-{yellow|orange|red}</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>ไอคอน 16 · กรอบ 16×24 ทุกที่ (ไม่มีวงกลม)</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>--text-danger-default / --surface-colorfulbadge-orange-bold</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>ไอคอน 14</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>src/components/badge/VitalAlertMark.jsx</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>WG1 OPD-21 · 22 ต.ค. 69</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>มีอาการทางจิต</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>ไอคอน psychology_alt (filled) สีส้ม</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>แพทย์ระบุหลังวินิจฉัยว่ามีอาการทางจิต — ต้องเฝ้าระวังขณะรอตรวจ</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>แพทย์ติ๊ก Checkbox "ผู้ป่วยรายนี้มีอาการทางจิต" ใต้การวินิจฉัย (เดิม: OAS ที่จุดคัดกรอง — เปลี่ยน 23 ต.ค. 69)</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>แพทย์ไม่ได้ติ๊ก · worklist เวชระเบียน เฉพาะรายใหม่</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>src/data/psychDoctorFlags.js · PsychDoctorFlag.jsx (DiagnosisColumn)</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>TooltipGroups: "มีอาการทางจิต" · "แพทย์ระบุหลังการวินิจฉัย" · ระบุโดย · เมื่อ · การเฝ้าระวัง</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>ไม่มี</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>--text-colorfulbadge-orange</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>ไอคอน 14 · กรอบ 16×24</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>src/components/badge/PsychMark.jsx</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
-        <is>
-          <t>onCard (ใช้บน PatientCard)</t>
-        </is>
-      </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>67-00016 · 67-00020 · 67-00013 · 67-00003 …</t>
-        </is>
-      </c>
-      <c r="O13" s="4" t="inlineStr">
-        <is>
-          <t>7 · 16 ต.ค. 69</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>showPsychMark</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>7 · 16 ต.ค. 69 · แก้ 23 ต.ค. 69</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Mobile Application</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>mobile_friendly สีเขียวอมฟ้า = มีบัญชี · mobile_off สีเทา = ลบบัญชีแล้ว</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>ผู้รับบริการมี/เคยมีบัญชีแอป BMA Health</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>มีบัญชี หรือเคยดาวน์โหลดแล้วลบ</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>ยังไม่มีบัญชี · showMobileApp={false}</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>src/data/mobileAppAccounts.js</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>TooltipGroups: ประวัติดาวน์โหลด/ลบบัญชี + เหตุผล</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>ไม่มี</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>--text-colorfulbadge-teal / -grey</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>ไอคอน 14</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>src/components/badge/MobileAppMark.jsx</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>showMobileApp</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>ผู้ใช้ 24 ต.ค. 69 ข้อ 5.1–5.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>ไอคอนเฉพาะหน้า (extraMarks)</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>ไอคอน 16px filled ของหน้านั้น ต่อท้ายสุด</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>ไอคอน 14px filled ของหน้านั้น ต่อท้ายสุด</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>ข้อมูลเฉพาะงาน เช่น กลุ่มโภชนาการ · เหตุผลการส่งต่อ/เด็กเสี่ยงของงานสังคมสงเคราะห์</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>หน้าส่ง prop extraMarks มา (ดูชีต "ไอคอนเฉพาะหน้า")</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>หน้าอื่นทั้งหมด</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>ตามหน้า</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>TooltipGroups ตามหน้า</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>ไม่มี</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>--text-colorfulbadge-{tone}</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>กรอบ 16×24</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>NutritionQueuePage.jsx (GroupMark) · social-work/SocialWorkShared.jsx (SwRiskMarks)</t>
         </is>
       </c>
-      <c r="M14" s="5" t="inlineStr">
+      <c r="M16" s="5" t="inlineStr">
         <is>
           <t>extraMarks</t>
         </is>
       </c>
-      <c r="N14" s="5" t="inlineStr">
+      <c r="N16" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O14" s="5" t="inlineStr">
+      <c r="O16" s="5" t="inlineStr">
         <is>
           <t>13 ต.ค. 69</t>
         </is>
@@ -1395,6 +1527,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1587,6 +1720,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1669,7 +1803,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>pregnant_woman filled สีชมพู 16px</t>
+          <t>pregnant_woman filled สีชมพู 14px</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -1854,7 +1988,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>หลังชื่อ: (ชื่อเรียก) · privacy_tip สีขาว · psychology_alt สีตามระดับ — ไอคอนอย่างเดียว ไม่มีวงกลม</t>
+          <t>หลังชื่อ: (ชื่อเรียก) · psychology_alt · Mobile App สีขาว — ไอคอนอย่างเดียว ไม่มีวงกลม</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1864,7 +1998,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>เกณฑ์เดียวกับชีต "ภาพรวม" ข้อ 1 · 6 · 8</t>
+          <t>เกณฑ์เดียวกับชีต "ภาพรวม" ข้อ 1 · มีอาการทางจิต · Mobile App</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1928,7 +2062,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>schedule filled สีเขียวแบรนด์ 16px</t>
+          <t>schedule filled สีเขียวแบรนด์ 14px</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1965,7 +2099,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>flag filled สีแดง 16px</t>
+          <t>flag filled สีแดง 14px</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -2150,7 +2284,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>lock filled ม่วง 16px</t>
+          <t>lock filled ม่วง 14px</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2187,7 +2321,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>lock filled ม่วง 16px</t>
+          <t>lock filled ม่วง 14px</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -2224,7 +2358,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>pregnant_woman filled ชมพู 16px</t>
+          <t>pregnant_woman filled ชมพู 14px</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2261,7 +2395,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>flag filled แดง 16px</t>
+          <t>flag filled แดง 14px</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -2298,7 +2432,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>pregnant_woman filled ส้ม 16px</t>
+          <t>pregnant_woman filled ส้ม 14px</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2335,7 +2469,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>radiology filled น้ำเงิน 16px</t>
+          <t>radiology filled น้ำเงิน 14px</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -2372,7 +2506,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>output filled ส้ม 16px</t>
+          <t>output filled ส้ม 14px</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2409,7 +2543,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>content_copy filled ส้ม 16px</t>
+          <t>content_copy filled ส้ม 14px</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -2446,7 +2580,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>flag filled แดง 16px</t>
+          <t>flag filled แดง 14px</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2483,7 +2617,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>monitor_weight filled ส้ม 16px</t>
+          <t>monitor_weight filled ส้ม 14px</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -2581,10 +2715,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1 เหตุผล = 1 ไอคอน · Material Symbols filled 16px · สีตามกลุ่ม</t>
-        </is>
-      </c>
-    </row>
+          <t>1 เหตุผล = 1 ไอคอน · Material Symbols filled 14px · สีตามกลุ่ม</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3488,7 +3623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3511,6 +3646,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3644,68 +3780,68 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>ไอคอนกลาง (ทุกหน้ารายชื่อ)</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>โรคที่อ่อนไหว</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>เวชระเบียน › โรคประจำตัว (mrPatients.chronicDiseases) · Problem list ของแพทย์ (treatmentProblemList) · ทะเบียนยา ARV (hivStiVisits)</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>รหัส B20–B24 หรือชื่อมีคำ HIV/เอชไอวี · รหัส C50 หรือชื่อมีคำ มะเร็งเต้านม · Problem list สถานะ active/watch · ARV สถานะ here/ltfu · และ role มีสิทธิ์ข้อมูลลับ (canSeeConfidential = true)</t>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>ฉุกเฉิน (แดง)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>จุดคัดกรอง OPD › ขั้น "ซักประวัติ" ช่อง ระดับการคัดแยก (Triage ESI) → screening.symptom.triage</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>triage.level = 1 หรือ 2 → ฉุกเฉิน (แดง)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>ไอคอนกลาง (ทุกหน้ารายชื่อ)</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>ฉุกเฉิน (แดง)</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>เร่งด่วน (ส้ม)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>จุดคัดกรอง OPD › ขั้น "ซักประวัติ" ช่อง ระดับการคัดแยก (Triage ESI) → screening.symptom.triage</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>triage.level = 1 หรือ 2 → ฉุกเฉิน (แดง)</t>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>triage.level = 3 → เร่งด่วน (ส้ม)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>ไอคอนกลาง (ทุกหน้ารายชื่อ)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>เร่งด่วน (ส้ม)</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>จุดคัดกรอง OPD › ขั้น "ซักประวัติ" ช่อง ระดับการคัดแยก (Triage ESI) → screening.symptom.triage</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>triage.level = 3 → เร่งด่วน (ส้ม)</t>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>มีอาการทางจิต</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>ห้องตรวจแพทย์ › ใต้การวินิจฉัย Checkbox "ผู้ป่วยรายนี้มีอาการทางจิต" → psychDoctorFlags.js</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>แพทย์ติ๊ก (เดิม: OAS ที่จุดคัดกรอง — เปลี่ยน 23 ต.ค. 69)</t>
         </is>
       </c>
     </row>
@@ -3717,61 +3853,61 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>มีอาการทางจิต (OAS)</t>
+          <t>สภาพที่มาใช้บริการ</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>จุดคัดกรอง OPD › ขั้น "แบบประเมิน" แถว แบบประเมินพฤติกรรมก้าวร้าว (OAS) → screening.behaviour.oasDetail</t>
+          <t>เวชระเบียน › ขั้น "หมายเหตุและ Flag" ช่อง สภาพที่มาใช้บริการ</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>oasDetail.status = "has" (มีอาการทางจิต) และระดับ = เหลือง / ส้ม / แดง (ไม่ระบุระดับ → คิดจากอาการที่ติ๊กสูงสุด) · เขียว/ไม่มีอาการ = ไม่แสดง</t>
+          <t>เปลนอน / นั่งรถเข็น = ไอคอน · อื่นๆ = คำสีแดง · เดิน = ไม่แสดง</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>ไอคอนเฉพาะหน้า</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>ก้าวร้าวพิเศษ</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>จุดคัดกรอง OPD › ขั้น "แบบประเมิน" → screening.behaviour.specialAggression</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>specialAggression = true และหมวดไม่ถูกข้าม · ⚠ ช่องติ๊กถูกถอดจากหน้าคัดกรองแล้ว (16 ต.ค. 69) — ขึ้นเฉพาะข้อมูลเก่า</t>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>ไอคอนกลาง (ทุกหน้ารายชื่อ)</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>สัญญาณชีพวิกฤต</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>จุดคัดกรอง OPD › สัญญาณชีพรอบล่าสุด</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>อันตราย ≥ 1 ค่า = แดง · เฝ้าระวัง ≥ 2 ค่า = ส้ม</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>ไอคอนเฉพาะหน้า</t>
+          <t>ไอคอนกลาง (ทุกหน้ารายชื่อ)</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ตั้งครรภ์</t>
+          <t>Mobile Application</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>จุดคัดกรอง OPD › ขั้น "ซักประวัติ" ช่อง สถานะการตั้งครรภ์ + LMP → screening.pregnancyStatus · lmp</t>
+          <t>บัญชีแอป BMA Health (mobileAppAccounts.js)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>pregnancyStatus = "กำลังตั้งครรภ์" (อายุครรภ์คิดจาก LMP)</t>
+          <t>มีบัญชี = mobile_friendly · ลบบัญชีแล้ว = mobile_off</t>
         </is>
       </c>
     </row>
@@ -3783,17 +3919,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>ความเสี่ยงสุขภาพจิต</t>
+          <t>ก้าวร้าวพิเศษ</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>เยี่ยมบ้าน › หน้าบันทึกการเยี่ยม แบบประเมิน 2Q plus / 9Q → ประวัติ homevisitMentalRisk (ผลล่าสุด)</t>
+          <t>จุดคัดกรอง OPD › ขั้น "แบบประเมิน" → screening.behaviour.specialAggression</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>เหลือง = 2Q plus บวก หรือ 9Q 7–12 · ส้ม = 9Q 13–18 · แดง = 2Q plus ข้อ 3 "มี" หรือ 9Q ข้อ 9 หรือ 9Q ≥ 19 · ไม่พบความเสี่ยง = ไม่แสดง</t>
+          <t>specialAggression = true และหมวดไม่ถูกข้าม · ⚠ ช่องติ๊กถูกถอดจากหน้าคัดกรองแล้ว (16 ต.ค. 69) — ขึ้นเฉพาะข้อมูลเก่า</t>
         </is>
       </c>
     </row>
@@ -3805,17 +3941,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>กลุ่มโภชนาการ</t>
+          <t>ตั้งครรภ์</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>งานโภชนาการ › เคสที่รับส่งต่อ ช่องกลุ่มเป้าหมาย → row.group</t>
+          <t>จุดคัดกรอง OPD › ขั้น "ซักประวัติ" ช่อง สถานะการตั้งครรภ์ + LMP → screening.pregnancyStatus · lmp</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>child = เด็ก · pregnant = หญิงตั้งครรภ์ · elderly = ผู้สูงอายุ · adult = ไม่มีไอคอน</t>
+          <t>pregnancyStatus = "กำลังตั้งครรภ์" (อายุครรภ์คิดจาก LMP)</t>
         </is>
       </c>
     </row>
@@ -3827,17 +3963,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>เหตุผลการส่งต่อ (33 แบบ)</t>
+          <t>ความเสี่ยงสุขภาพจิต</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>ป๊อปอัปส่งต่อถึงงานสังคมสงเคราะห์ (ติ๊กเหตุผล) · เวชระเบียน/วัคซีน/คัดกรอง (เด็กเสี่ยง) → row.referralWatchTags · referralOtherReason · childAlerts</t>
+          <t>เยี่ยมบ้าน › หน้าบันทึกการเยี่ยม แบบประเมิน 2Q plus / 9Q → ประวัติ homevisitMentalRisk (ผลล่าสุด)</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>1 ค่าที่ติ๊ก = 1 ไอคอน · เด็กเสี่ยงเฉพาะอายุ &lt; 18 ปี: ไม่มีสิทธิการรักษา · ไม่ได้วัคซีนตามวัย · สงสัยถูกกระทำรุนแรง</t>
+          <t>เหลือง = 2Q plus บวก หรือ 9Q 7–12 · ส้ม = 9Q 13–18 · แดง = 2Q plus ข้อ 3 "มี" หรือ 9Q ข้อ 9 หรือ 9Q ≥ 19 · ไม่พบความเสี่ยง = ไม่แสดง</t>
         </is>
       </c>
     </row>
@@ -3849,17 +3985,17 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>ป้าย "ใหม่"</t>
+          <t>กลุ่มโภชนาการ</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>คิวเวชระเบียน › แถว walk-in ที่ยังไม่มี HN</t>
+          <t>งานโภชนาการ › เคสที่รับส่งต่อ ช่องกลุ่มเป้าหมาย → row.group</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>isNewPatientRow(row) = true</t>
+          <t>child = เด็ก · pregnant = หญิงตั้งครรภ์ · elderly = ผู้สูงอายุ · adult = ไม่มีไอคอน</t>
         </is>
       </c>
     </row>
@@ -3871,17 +4007,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>อยู่ในการติดตามการดูแล</t>
+          <t>เหตุผลการส่งต่อ (33 แบบ)</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>คลินิกโรคเรื้อรัง › ขึ้นทะเบียนผู้ป่วย (chronic registration) + ประวัติการมาคลินิก</t>
+          <t>ป๊อปอัปส่งต่อถึงงานสังคมสงเคราะห์ (ติ๊กเหตุผล) · เวชระเบียน/วัคซีน/คัดกรอง (เด็กเสี่ยง) → row.referralWatchTags · referralOtherReason · childAlerts</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>มีทะเบียนแล้ว หรือจำนวนครั้งที่มาคลินิก &gt; 0</t>
+          <t>1 ค่าที่ติ๊ก = 1 ไอคอน · เด็กเสี่ยงเฉพาะอายุ &lt; 18 ปี: ไม่มีสิทธิการรักษา · ไม่ได้วัคซีนตามวัย · สงสัยถูกกระทำรุนแรง</t>
         </is>
       </c>
     </row>
@@ -3893,17 +4029,17 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Red Flag พัฒนาการ</t>
+          <t>ป้าย "ใหม่"</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>คลินิกเด็กดี › แบบประเมินพัฒนาการ DSPM / DAIM (developmentClinic.js)</t>
+          <t>คิวเวชระเบียน › แถว walk-in ที่ยังไม่มี HN</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>พบพัฒนาการล่าช้า และเข้าเกณฑ์ Red Flag (getDevRedFlag → active = true)</t>
+          <t>isNewPatientRow(row) = true</t>
         </is>
       </c>
     </row>
@@ -3915,17 +4051,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>มาฟังผล</t>
+          <t>อยู่ในการติดตามการดูแล</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>ป๊อปอัป "ยืนยันรับผู้ป่วย" ที่จุดคัดกรอง ติ๊ก "มาฟังผล" → resultsVisits.js</t>
+          <t>คลินิกโรคเรื้อรัง › ขึ้นทะเบียนผู้ป่วย (chronic registration) + ประวัติการมาคลินิก</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>มีแถว resultsVisit ของ HN วันนี้</t>
+          <t>มีทะเบียนแล้ว หรือจำนวนครั้งที่มาคลินิก &gt; 0</t>
         </is>
       </c>
     </row>
@@ -3937,17 +4073,17 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>ข้อมูลลับ (นักเรียน)</t>
+          <t>Red Flag พัฒนาการ</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>ทะเบียนนักเรียน › ข้อมูลนักเรียน → student.confidential</t>
+          <t>คลินิกเด็กดี › แบบประเมินพัฒนาการ DSPM / DAIM (developmentClinic.js)</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>confidential = true</t>
+          <t>พบพัฒนาการล่าช้า และเข้าเกณฑ์ Red Flag (getDevRedFlag → active = true)</t>
         </is>
       </c>
     </row>
@@ -3959,17 +4095,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>เสียชีวิต</t>
+          <t>มาฟังผล</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>เวชระเบียน › สถานะการมีชีวิต → patient.lifeStatus</t>
+          <t>ป๊อปอัป "ยืนยันรับผู้ป่วย" ที่จุดคัดกรอง ติ๊ก "มาฟังผล" → resultsVisits.js</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>lifeStatus = "deceased"</t>
+          <t>มีแถว resultsVisit ของ HN วันนี้</t>
         </is>
       </c>
     </row>
@@ -3981,17 +4117,17 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>กำลังดู</t>
+          <t>ข้อมูลลับ (นักเรียน)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>สถานะหน้าจอ (ไม่ได้มาจากข้อมูลผู้ป่วย)</t>
+          <t>ทะเบียนนักเรียน › ข้อมูลนักเรียน → student.confidential</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>แถวที่เปิดแผงรายละเอียดอยู่</t>
+          <t>confidential = true</t>
         </is>
       </c>
     </row>
@@ -4003,15 +4139,59 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
+          <t>เสียชีวิต</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>เวชระเบียน › สถานะการมีชีวิต → patient.lifeStatus</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>lifeStatus = "deceased"</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>ไอคอนเฉพาะหน้า</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>กำลังดู</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>สถานะหน้าจอ (ไม่ได้มาจากข้อมูลผู้ป่วย)</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>แถวที่เปิดแผงรายละเอียดอยู่</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>ไอคอนเฉพาะหน้า</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
           <t>ป้าย HN</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>HN ของแถว</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>แสดงทุกแถว</t>
         </is>
@@ -4021,4 +4201,367 @@
   <autoFilter ref="A4:D26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ประวัติการแก้ไข — ไอคอนหลังชื่อผู้รับบริการ</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ล่าสุดก่อน · เหตุผลอ้างตามคำสั่งผู้ใช้ / decision log / คอมเมนต์ในโค้ด</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>วันที่</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>ประเภท</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>เปลี่ยนอะไร</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>เหตุผล / ที่มา</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>24 ต.ค. 69</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>เอกสาร</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>ลบไอคอนโรคที่อ่อนไหว (B24) ออกจากเอกสาร · เพิ่มไอคอนใหม่ 4 แบบ · แถวอาการทางจิตใหม่ · ขนาด 14px</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>ผู้ใช้สั่ง 24 ต.ค. 69 "ลบ icon b24 ออก · อัปเดท icon หลังชื่อทั้งหมด"</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>24 ต.ค. 69</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>เพิ่ม</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>ไอคอน Mobile Application (mobile_friendly / mobile_off) ทุก worklist + การ์ดเขียว</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>ให้เจ้าหน้าที่แนะนำคนที่ยังไม่มีแอปให้ดาวน์โหลด (ผู้ใช้ 24 ต.ค. 69 ข้อ 5.1–5.2)</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>804c6ba9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>23 ต.ค. 69</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>เพิ่ม</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>สภาพที่มาใช้บริการ: เปลนอน · นั่งรถเข็น · อื่นๆ คำสีแดง · ลำดับคิว ฉุกเฉิน → เปลนอน → รถเข็น → เร่งด่วน</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>ผู้ใช้: เลือก Flag นั่งรถเข็น/เปลนอนต้องแสดง icon หลังชื่อ · อื่นๆ แสดงคำสีแดงแต่ไม่ให้ Priority · ทุก worklist ให้เป็น Priority อันดับแรก</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>14ea566b</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>23 ต.ค. 69</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>แก้</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>ไอคอนเปลนอน → airline_seat_flat</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>ไอคอนเดิม self_improvement ดูเหมือนคนนั่งสมาธิ</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>14ea566b</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>23 ต.ค. 69</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>แก้</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>ไอคอนหลังชื่อทุกตัว 16 → 14px</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>ผู้ใช้: "เล็กลงอีกนิด"</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>14ea566b</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>23 ต.ค. 69</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>ลบ</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>ไอคอนโรคที่อ่อนไหว (privacy_tip · B24) จากทุก worklist และการ์ดเขียว</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>ผู้ใช้: "ลบสัญลักษณ์ HIV ออก" · ไม่ได้บันทึกเหตุผลเพิ่ม</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>7c45887f</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>23 ต.ค. 69</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>แก้</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>อาการทางจิต: จาก OAS ที่จุดคัดกรอง → แพทย์ติ๊กหลังวินิจฉัย · สีส้มสีเดียว</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>decision log 23 ต.ค. 69 · ไม่ได้บันทึกเหตุผล</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>7c45887f</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>22 ต.ค. 69</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>เพิ่ม</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>สัญญาณชีพวิกฤต (แดง) / ผิดปกติหลายค่า (ส้ม)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>WG1 OPD-21 · นอก TOR</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>1484d2b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>22 ต.ค. 69</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>เพิ่ม</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>/treat: ผลตรวจรอเปิดอ่านหลังชื่อแทนคอลัมน์ · มาฟังผลย้ายใต้ชื่อ</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>WG1 "ดูง่าย ไม่รก" · คอลัมน์เดิมดัน CC ตกจอ</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>58a9bfa0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>22 ต.ค. 69</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>ลบ</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>แถบสีระดับคัดแยกหน้าชื่อ (TriageLevelBar)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>ไม่ได้บันทึกเหตุผล</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>1484d2b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>20 ต.ค. 69</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>เอกสาร</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>ฉบับแรก</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/worklist-name-icons.xlsx
+++ b/worklist-name-icons.xlsx
@@ -1228,7 +1228,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>ค่าปกติ · ยังไม่คัดกรอง · ตอนนี้ขึ้นเฉพาะรายที่มีไอคอนฉุกเฉิน/เร่งด่วนด้วย (รอยืนยัน)</t>
+          <t>ค่าปกติ · ยังไม่คัดกรอง · worklist เวชระเบียน · ขึ้นทุกรายที่ค่าเกินเกณฑ์ ไม่ขึ้นกับ ESI (แก้ 24 ต.ค. 69)</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -4209,7 +4209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4237,6 +4237,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4272,17 +4273,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>เอกสาร</t>
+          <t>แก้</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>ลบไอคอนโรคที่อ่อนไหว (B24) ออกจากเอกสาร · เพิ่มไอคอนใหม่ 4 แบบ · แถวอาการทางจิตใหม่ · ขนาด 14px</t>
+          <t>ไอคอนสัญญาณชีพวิกฤตขึ้นทุกรายที่ค่าเกินเกณฑ์ (เดิมเฉพาะรายฉุกเฉิน/เร่งด่วน)</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>ผู้ใช้สั่ง 24 ต.ค. 69 "ลบ icon b24 ออก · อัปเดท icon หลังชื่อทั้งหมด"</t>
+          <t>ค่าวิกฤตแต่ ESI 4–5 เดิมไม่เห็นไอคอน · ผู้ใช้เลือก 2ก</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -4299,29 +4300,29 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>เพิ่ม</t>
+          <t>เอกสาร</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>ไอคอน Mobile Application (mobile_friendly / mobile_off) ทุก worklist + การ์ดเขียว</t>
+          <t>ลบไอคอนโรคที่อ่อนไหว (B24) ออกจากเอกสาร · เพิ่มไอคอนใหม่ 4 แบบ · แถวอาการทางจิตใหม่ · ขนาด 14px</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>ให้เจ้าหน้าที่แนะนำคนที่ยังไม่มีแอปให้ดาวน์โหลด (ผู้ใช้ 24 ต.ค. 69 ข้อ 5.1–5.2)</t>
+          <t>ผู้ใช้สั่ง 24 ต.ค. 69 "ลบ icon b24 ออก · อัปเดท icon หลังชื่อทั้งหมด"</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>804c6ba9</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>23 ต.ค. 69</t>
+          <t>24 ต.ค. 69</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -4331,17 +4332,17 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>สภาพที่มาใช้บริการ: เปลนอน · นั่งรถเข็น · อื่นๆ คำสีแดง · ลำดับคิว ฉุกเฉิน → เปลนอน → รถเข็น → เร่งด่วน</t>
+          <t>ไอคอน Mobile Application (mobile_friendly / mobile_off) ทุก worklist + การ์ดเขียว</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>ผู้ใช้: เลือก Flag นั่งรถเข็น/เปลนอนต้องแสดง icon หลังชื่อ · อื่นๆ แสดงคำสีแดงแต่ไม่ให้ Priority · ทุก worklist ให้เป็น Priority อันดับแรก</t>
+          <t>ให้เจ้าหน้าที่แนะนำคนที่ยังไม่มีแอปให้ดาวน์โหลด (ผู้ใช้ 24 ต.ค. 69 ข้อ 5.1–5.2)</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>14ea566b</t>
+          <t>804c6ba9</t>
         </is>
       </c>
     </row>
@@ -4353,17 +4354,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>แก้</t>
+          <t>เพิ่ม</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>ไอคอนเปลนอน → airline_seat_flat</t>
+          <t>สภาพที่มาใช้บริการ: เปลนอน · นั่งรถเข็น · อื่นๆ คำสีแดง · ลำดับคิว ฉุกเฉิน → เปลนอน → รถเข็น → เร่งด่วน</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>ไอคอนเดิม self_improvement ดูเหมือนคนนั่งสมาธิ</t>
+          <t>ผู้ใช้: เลือก Flag นั่งรถเข็น/เปลนอนต้องแสดง icon หลังชื่อ · อื่นๆ แสดงคำสีแดงแต่ไม่ให้ Priority · ทุก worklist ให้เป็น Priority อันดับแรก</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -4385,12 +4386,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>ไอคอนหลังชื่อทุกตัว 16 → 14px</t>
+          <t>ไอคอนเปลนอน → airline_seat_flat</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>ผู้ใช้: "เล็กลงอีกนิด"</t>
+          <t>ไอคอนเดิม self_improvement ดูเหมือนคนนั่งสมาธิ</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -4407,22 +4408,22 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>ลบ</t>
+          <t>แก้</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>ไอคอนโรคที่อ่อนไหว (privacy_tip · B24) จากทุก worklist และการ์ดเขียว</t>
+          <t>ไอคอนหลังชื่อทุกตัว 16 → 14px</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>ผู้ใช้: "ลบสัญลักษณ์ HIV ออก" · ไม่ได้บันทึกเหตุผลเพิ่ม</t>
+          <t>ผู้ใช้: "เล็กลงอีกนิด"</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>7c45887f</t>
+          <t>14ea566b</t>
         </is>
       </c>
     </row>
@@ -4434,17 +4435,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>แก้</t>
+          <t>ลบ</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>อาการทางจิต: จาก OAS ที่จุดคัดกรอง → แพทย์ติ๊กหลังวินิจฉัย · สีส้มสีเดียว</t>
+          <t>ไอคอนโรคที่อ่อนไหว (privacy_tip · B24) จากทุก worklist และการ์ดเขียว</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>decision log 23 ต.ค. 69 · ไม่ได้บันทึกเหตุผล</t>
+          <t>ผู้ใช้: "ลบสัญลักษณ์ HIV ออก" · ไม่ได้บันทึกเหตุผลเพิ่ม</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -4456,27 +4457,27 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>22 ต.ค. 69</t>
+          <t>23 ต.ค. 69</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>เพิ่ม</t>
+          <t>แก้</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>สัญญาณชีพวิกฤต (แดง) / ผิดปกติหลายค่า (ส้ม)</t>
+          <t>อาการทางจิต: จาก OAS ที่จุดคัดกรอง → แพทย์ติ๊กหลังวินิจฉัย · สีส้มสีเดียว</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>WG1 OPD-21 · นอก TOR</t>
+          <t>decision log 23 ต.ค. 69 · ไม่ได้บันทึกเหตุผล</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>1484d2b6</t>
+          <t>7c45887f</t>
         </is>
       </c>
     </row>
@@ -4493,17 +4494,17 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>/treat: ผลตรวจรอเปิดอ่านหลังชื่อแทนคอลัมน์ · มาฟังผลย้ายใต้ชื่อ</t>
+          <t>สัญญาณชีพวิกฤต (แดง) / ผิดปกติหลายค่า (ส้ม)</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>WG1 "ดูง่าย ไม่รก" · คอลัมน์เดิมดัน CC ตกจอ</t>
+          <t>WG1 OPD-21 · นอก TOR</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>58a9bfa0</t>
+          <t>1484d2b6</t>
         </is>
       </c>
     </row>
@@ -4515,47 +4516,74 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>ลบ</t>
+          <t>เพิ่ม</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>แถบสีระดับคัดแยกหน้าชื่อ (TriageLevelBar)</t>
+          <t>/treat: ผลตรวจรอเปิดอ่านหลังชื่อแทนคอลัมน์ · มาฟังผลย้ายใต้ชื่อ</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>ไม่ได้บันทึกเหตุผล</t>
+          <t>WG1 "ดูง่าย ไม่รก" · คอลัมน์เดิมดัน CC ตกจอ</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>1484d2b6</t>
+          <t>58a9bfa0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
+          <t>22 ต.ค. 69</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>ลบ</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>แถบสีระดับคัดแยกหน้าชื่อ (TriageLevelBar)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>ไม่ได้บันทึกเหตุผล</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>1484d2b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
           <t>20 ต.ค. 69</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>เอกสาร</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>ฉบับแรก</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/worklist-name-icons.xlsx
+++ b/worklist-name-icons.xlsx
@@ -1355,7 +1355,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>mobile_friendly สีเขียวอมฟ้า = มีบัญชี · mobile_off สีเทา = ลบบัญชีแล้ว</t>
+          <t>mobile_friendly / mobile_off แบบเส้น (outline · weight 600) · เขียวอมฟ้า = มีบัญชี · เทา = ลบบัญชีแล้ว</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1527,7 +1527,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1720,7 +1719,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2719,7 +2717,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3646,7 +3643,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4209,7 +4205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4237,7 +4233,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4268,7 +4263,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>24 ต.ค. 69</t>
+          <t>25 ต.ค. 69</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -4278,12 +4273,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>ไอคอนสัญญาณชีพวิกฤตขึ้นทุกรายที่ค่าเกินเกณฑ์ (เดิมเฉพาะรายฉุกเฉิน/เร่งด่วน)</t>
+          <t>ไอคอน Mobile Application แบบทึบ → แบบเส้น 14px</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>ค่าวิกฤตแต่ ESI 4–5 เดิมไม่เห็นไอคอน · ผู้ใช้เลือก 2ก</t>
+          <t>แบบทึบเห็นเครื่องหมายถูก/ขีดฆ่าไม่ชัด · ผู้ใช้ "ปรับรูป mobile ให้ดูง่ายกว่านี้"</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -4300,17 +4295,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>เอกสาร</t>
+          <t>แก้</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>ลบไอคอนโรคที่อ่อนไหว (B24) ออกจากเอกสาร · เพิ่มไอคอนใหม่ 4 แบบ · แถวอาการทางจิตใหม่ · ขนาด 14px</t>
+          <t>ไอคอนสัญญาณชีพวิกฤตขึ้นทุกรายที่ค่าเกินเกณฑ์ (เดิมเฉพาะรายฉุกเฉิน/เร่งด่วน)</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>ผู้ใช้สั่ง 24 ต.ค. 69 "ลบ icon b24 ออก · อัปเดท icon หลังชื่อทั้งหมด"</t>
+          <t>ค่าวิกฤตแต่ ESI 4–5 เดิมไม่เห็นไอคอน · ผู้ใช้เลือก 2ก</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -4327,29 +4322,29 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>เพิ่ม</t>
+          <t>เอกสาร</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>ไอคอน Mobile Application (mobile_friendly / mobile_off) ทุก worklist + การ์ดเขียว</t>
+          <t>ลบไอคอนโรคที่อ่อนไหว (B24) ออกจากเอกสาร · เพิ่มไอคอนใหม่ 4 แบบ · แถวอาการทางจิตใหม่ · ขนาด 14px</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>ให้เจ้าหน้าที่แนะนำคนที่ยังไม่มีแอปให้ดาวน์โหลด (ผู้ใช้ 24 ต.ค. 69 ข้อ 5.1–5.2)</t>
+          <t>ผู้ใช้สั่ง 24 ต.ค. 69 "ลบ icon b24 ออก · อัปเดท icon หลังชื่อทั้งหมด"</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>804c6ba9</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>23 ต.ค. 69</t>
+          <t>24 ต.ค. 69</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -4359,17 +4354,17 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>สภาพที่มาใช้บริการ: เปลนอน · นั่งรถเข็น · อื่นๆ คำสีแดง · ลำดับคิว ฉุกเฉิน → เปลนอน → รถเข็น → เร่งด่วน</t>
+          <t>ไอคอน Mobile Application (mobile_friendly / mobile_off) ทุก worklist + การ์ดเขียว</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>ผู้ใช้: เลือก Flag นั่งรถเข็น/เปลนอนต้องแสดง icon หลังชื่อ · อื่นๆ แสดงคำสีแดงแต่ไม่ให้ Priority · ทุก worklist ให้เป็น Priority อันดับแรก</t>
+          <t>ให้เจ้าหน้าที่แนะนำคนที่ยังไม่มีแอปให้ดาวน์โหลด (ผู้ใช้ 24 ต.ค. 69 ข้อ 5.1–5.2)</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>14ea566b</t>
+          <t>804c6ba9</t>
         </is>
       </c>
     </row>
@@ -4381,17 +4376,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>แก้</t>
+          <t>เพิ่ม</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>ไอคอนเปลนอน → airline_seat_flat</t>
+          <t>สภาพที่มาใช้บริการ: เปลนอน · นั่งรถเข็น · อื่นๆ คำสีแดง · ลำดับคิว ฉุกเฉิน → เปลนอน → รถเข็น → เร่งด่วน</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>ไอคอนเดิม self_improvement ดูเหมือนคนนั่งสมาธิ</t>
+          <t>ผู้ใช้: เลือก Flag นั่งรถเข็น/เปลนอนต้องแสดง icon หลังชื่อ · อื่นๆ แสดงคำสีแดงแต่ไม่ให้ Priority · ทุก worklist ให้เป็น Priority อันดับแรก</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -4413,12 +4408,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>ไอคอนหลังชื่อทุกตัว 16 → 14px</t>
+          <t>ไอคอนเปลนอน → airline_seat_flat</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>ผู้ใช้: "เล็กลงอีกนิด"</t>
+          <t>ไอคอนเดิม self_improvement ดูเหมือนคนนั่งสมาธิ</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -4435,22 +4430,22 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>ลบ</t>
+          <t>แก้</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>ไอคอนโรคที่อ่อนไหว (privacy_tip · B24) จากทุก worklist และการ์ดเขียว</t>
+          <t>ไอคอนหลังชื่อทุกตัว 16 → 14px</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>ผู้ใช้: "ลบสัญลักษณ์ HIV ออก" · ไม่ได้บันทึกเหตุผลเพิ่ม</t>
+          <t>ผู้ใช้: "เล็กลงอีกนิด"</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>7c45887f</t>
+          <t>14ea566b</t>
         </is>
       </c>
     </row>
@@ -4462,17 +4457,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>แก้</t>
+          <t>ลบ</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>อาการทางจิต: จาก OAS ที่จุดคัดกรอง → แพทย์ติ๊กหลังวินิจฉัย · สีส้มสีเดียว</t>
+          <t>ไอคอนโรคที่อ่อนไหว (privacy_tip · B24) จากทุก worklist และการ์ดเขียว</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>decision log 23 ต.ค. 69 · ไม่ได้บันทึกเหตุผล</t>
+          <t>ผู้ใช้: "ลบสัญลักษณ์ HIV ออก" · ไม่ได้บันทึกเหตุผลเพิ่ม</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -4484,27 +4479,27 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>22 ต.ค. 69</t>
+          <t>23 ต.ค. 69</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>เพิ่ม</t>
+          <t>แก้</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>สัญญาณชีพวิกฤต (แดง) / ผิดปกติหลายค่า (ส้ม)</t>
+          <t>อาการทางจิต: จาก OAS ที่จุดคัดกรอง → แพทย์ติ๊กหลังวินิจฉัย · สีส้มสีเดียว</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>WG1 OPD-21 · นอก TOR</t>
+          <t>decision log 23 ต.ค. 69 · ไม่ได้บันทึกเหตุผล</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>1484d2b6</t>
+          <t>7c45887f</t>
         </is>
       </c>
     </row>
@@ -4521,17 +4516,17 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>/treat: ผลตรวจรอเปิดอ่านหลังชื่อแทนคอลัมน์ · มาฟังผลย้ายใต้ชื่อ</t>
+          <t>สัญญาณชีพวิกฤต (แดง) / ผิดปกติหลายค่า (ส้ม)</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>WG1 "ดูง่าย ไม่รก" · คอลัมน์เดิมดัน CC ตกจอ</t>
+          <t>WG1 OPD-21 · นอก TOR</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>58a9bfa0</t>
+          <t>1484d2b6</t>
         </is>
       </c>
     </row>
@@ -4543,47 +4538,74 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>ลบ</t>
+          <t>เพิ่ม</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>แถบสีระดับคัดแยกหน้าชื่อ (TriageLevelBar)</t>
+          <t>/treat: ผลตรวจรอเปิดอ่านหลังชื่อแทนคอลัมน์ · มาฟังผลย้ายใต้ชื่อ</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>ไม่ได้บันทึกเหตุผล</t>
+          <t>WG1 "ดูง่าย ไม่รก" · คอลัมน์เดิมดัน CC ตกจอ</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>1484d2b6</t>
+          <t>58a9bfa0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>22 ต.ค. 69</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>ลบ</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>แถบสีระดับคัดแยกหน้าชื่อ (TriageLevelBar)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>ไม่ได้บันทึกเหตุผล</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>1484d2b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
           <t>20 ต.ค. 69</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>เอกสาร</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>ฉบับแรก</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
